--- a/e2e/expectedData/sub_Payroll_List.xlsx
+++ b/e2e/expectedData/sub_Payroll_List.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="107">
   <si>
     <t>DAFTAR PERHITUNGAN GAJI KARYAWAN</t>
   </si>
@@ -80,204 +80,210 @@
     <t>TAX</t>
   </si>
   <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>Customer Care Manager (PJ)</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>$ 200.00</t>
+  </si>
+  <si>
+    <t>$ 50.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>$ 13.94</t>
+  </si>
+  <si>
+    <t>$ 1.00</t>
+  </si>
+  <si>
+    <t>$ 314.94</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>$ 510.00</t>
+  </si>
+  <si>
+    <t>$ 10.00</t>
+  </si>
+  <si>
+    <t>$ 521.00</t>
+  </si>
+  <si>
+    <t>$ 52.10</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Service Solution Support Officer</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>$ 150.00</t>
+  </si>
+  <si>
+    <t>$ 8.26</t>
+  </si>
+  <si>
+    <t>$ 219.26</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>$ 300.00</t>
+  </si>
+  <si>
+    <t>$ 30.00</t>
+  </si>
+  <si>
+    <t>$ 85.00</t>
+  </si>
+  <si>
+    <t>$ 455.00</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>Business Planning &amp; Performance Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 500.00</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>$ 70.10</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>Quality Assuance Senior Engineer</t>
+  </si>
+  <si>
+    <t>$ 13.00</t>
+  </si>
+  <si>
+    <t>$ 36.00</t>
+  </si>
+  <si>
+    <t>$ 60.00</t>
+  </si>
+  <si>
+    <t>$ 817.58</t>
+  </si>
+  <si>
+    <t>$ 262.50</t>
+  </si>
+  <si>
+    <t>$ 1,189.08</t>
+  </si>
+  <si>
+    <t>$ 68.91</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>$ 505.00</t>
+  </si>
+  <si>
+    <t>$ 50.50</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>VP Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>O&amp;M Network Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 20.00</t>
+  </si>
+  <si>
+    <t>$ 42.59</t>
+  </si>
+  <si>
+    <t>$ 383.59</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Ermera</t>
+  </si>
+  <si>
+    <t>$ 561.00</t>
+  </si>
+  <si>
+    <t>$ 56.10</t>
+  </si>
+  <si>
     <t>ADROALDINO DA SILVA NORONHA TOME</t>
   </si>
   <si>
     <t>Customer Service Staff Manufahi</t>
   </si>
   <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
     <t>$ 120.00</t>
   </si>
   <si>
-    <t>$ 10.00</t>
-  </si>
-  <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
-    <t>$ 50.00</t>
-  </si>
-  <si>
     <t>$ 45.44</t>
   </si>
   <si>
-    <t>$ 1.00</t>
-  </si>
-  <si>
     <t>$ 356.44</t>
   </si>
   <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Ermera</t>
-  </si>
-  <si>
-    <t>$ 500.00</t>
-  </si>
-  <si>
-    <t>$ 561.00</t>
-  </si>
-  <si>
-    <t>$ 56.10</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>$ 30.00</t>
-  </si>
-  <si>
-    <t>$ 85.00</t>
-  </si>
-  <si>
-    <t>$ 455.00</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>Service Solution Support Officer</t>
-  </si>
-  <si>
-    <t>$ 150.00</t>
-  </si>
-  <si>
-    <t>$ 8.26</t>
-  </si>
-  <si>
-    <t>$ 219.26</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>Customer Care Manager (PJ)</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>$ 200.00</t>
-  </si>
-  <si>
-    <t>$ 13.94</t>
-  </si>
-  <si>
-    <t>$ 314.94</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 510.00</t>
-  </si>
-  <si>
-    <t>$ 521.00</t>
-  </si>
-  <si>
-    <t>$ 52.10</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>Business Planning &amp; Performance Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
-  </si>
-  <si>
-    <t>$ 70.10</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>VP Marketing &amp; Sales</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>Quality Assuance Senior Engineer</t>
-  </si>
-  <si>
-    <t>$ 13.00</t>
-  </si>
-  <si>
-    <t>$ 36.00</t>
-  </si>
-  <si>
-    <t>$ 60.00</t>
-  </si>
-  <si>
-    <t>$ 666.61</t>
-  </si>
-  <si>
-    <t>$ 262.50</t>
-  </si>
-  <si>
-    <t>$ 1,038.11</t>
-  </si>
-  <si>
-    <t>$ 103.81</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>O&amp;M Network Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 20.00</t>
-  </si>
-  <si>
-    <t>$ 42.59</t>
-  </si>
-  <si>
-    <t>$ 383.59</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>$ 505.00</t>
-  </si>
-  <si>
-    <t>$ 50.50</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -311,13 +317,13 @@
     <t>$ 347.50</t>
   </si>
   <si>
-    <t>$ 5,756.34</t>
-  </si>
-  <si>
-    <t>$ 402.71</t>
-  </si>
-  <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>$ 5,907.31</t>
+  </si>
+  <si>
+    <t>$ 367.81</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -848,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>24016</v>
+        <v>79001</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>21</v>
@@ -869,34 +875,34 @@
         <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>27</v>
@@ -907,16 +913,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>24</v>
@@ -925,7 +931,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>27</v>
@@ -934,7 +940,7 @@
         <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>27</v>
@@ -946,7 +952,7 @@
         <v>27</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>27</v>
@@ -955,10 +961,10 @@
         <v>27</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -966,25 +972,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>92003</v>
+        <v>24005</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>27</v>
@@ -993,28 +999,28 @@
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S7" s="3" t="s">
         <v>27</v>
@@ -1025,25 +1031,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>24005</v>
+        <v>92003</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>27</v>
@@ -1052,28 +1058,28 @@
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>27</v>
@@ -1084,28 +1090,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>27</v>
@@ -1117,13 +1123,13 @@
         <v>27</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>27</v>
@@ -1132,10 +1138,10 @@
         <v>27</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1143,25 +1149,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>95008</v>
+        <v>81010</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>27</v>
@@ -1173,28 +1179,28 @@
         <v>27</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1202,34 +1208,34 @@
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>91009</v>
+        <v>999999</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>27</v>
@@ -1241,7 +1247,7 @@
         <v>27</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>27</v>
@@ -1250,10 +1256,10 @@
         <v>27</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1264,28 +1270,28 @@
         <v>74003</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>27</v>
@@ -1300,7 +1306,7 @@
         <v>27</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>27</v>
@@ -1309,10 +1315,10 @@
         <v>27</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1320,58 +1326,58 @@
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>81010</v>
+        <v>91015</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="G13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1379,46 +1385,46 @@
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>91015</v>
+        <v>26013</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>27</v>
@@ -1427,10 +1433,10 @@
         <v>27</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1438,46 +1444,46 @@
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>999999</v>
+        <v>24016</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>27</v>
@@ -1486,15 +1492,15 @@
         <v>27</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1502,43 +1508,43 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="Q16" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S16" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -1546,7 +1552,7 @@
     </row>
     <row r="18" spans="1:19">
       <c r="A18" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -1569,7 +1575,7 @@
     </row>
     <row r="19" spans="1:19">
       <c r="A19" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -1580,7 +1586,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -1598,7 +1604,7 @@
     </row>
     <row r="21" spans="1:19">
       <c r="A21" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1609,7 +1615,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="7" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -1623,7 +1629,7 @@
     </row>
     <row r="22" spans="1:19">
       <c r="A22" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -1634,7 +1640,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>

--- a/e2e/expectedData/sub_Payroll_List.xlsx
+++ b/e2e/expectedData/sub_Payroll_List.xlsx
@@ -80,33 +80,165 @@
     <t>TAX</t>
   </si>
   <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>Business Planning &amp; Performance Senior Manager</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>$ 500.00</t>
+  </si>
+  <si>
+    <t>$ 150.00</t>
+  </si>
+  <si>
+    <t>$ 50.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>$ 1.00</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>$ 70.10</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>$ 505.00</t>
+  </si>
+  <si>
+    <t>$ 50.50</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>VP Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>O&amp;M Network Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 200.00</t>
+  </si>
+  <si>
+    <t>$ 20.00</t>
+  </si>
+  <si>
+    <t>$ 30.00</t>
+  </si>
+  <si>
+    <t>$ 42.59</t>
+  </si>
+  <si>
+    <t>$ 10.00</t>
+  </si>
+  <si>
+    <t>$ 383.59</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Ermera</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>$ 561.00</t>
+  </si>
+  <si>
+    <t>$ 56.10</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Manufahi</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>$ 120.00</t>
+  </si>
+  <si>
+    <t>$ 45.44</t>
+  </si>
+  <si>
+    <t>$ 356.44</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>$ 300.00</t>
+  </si>
+  <si>
+    <t>$ 85.00</t>
+  </si>
+  <si>
+    <t>$ 455.00</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Service Solution Support Officer</t>
+  </si>
+  <si>
+    <t>$ 8.26</t>
+  </si>
+  <si>
+    <t>$ 219.26</t>
+  </si>
+  <si>
     <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
     <t>Customer Care Manager (PJ)</t>
   </si>
   <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>$ 200.00</t>
-  </si>
-  <si>
-    <t>$ 50.00</t>
-  </si>
-  <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
     <t>$ 13.94</t>
   </si>
   <si>
-    <t>$ 1.00</t>
-  </si>
-  <si>
     <t>$ 314.94</t>
   </si>
   <si>
@@ -116,78 +248,15 @@
     <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
   </si>
   <si>
-    <t>IV</t>
-  </si>
-  <si>
     <t>$ 510.00</t>
   </si>
   <si>
-    <t>$ 10.00</t>
-  </si>
-  <si>
     <t>$ 521.00</t>
   </si>
   <si>
     <t>$ 52.10</t>
   </si>
   <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>Service Solution Support Officer</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>Outsource</t>
-  </si>
-  <si>
-    <t>$ 150.00</t>
-  </si>
-  <si>
-    <t>$ 8.26</t>
-  </si>
-  <si>
-    <t>$ 219.26</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>$ 30.00</t>
-  </si>
-  <si>
-    <t>$ 85.00</t>
-  </si>
-  <si>
-    <t>$ 455.00</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>Business Planning &amp; Performance Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 500.00</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
-  </si>
-  <si>
-    <t>$ 70.10</t>
-  </si>
-  <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
@@ -215,75 +284,6 @@
     <t>$ 68.91</t>
   </si>
   <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>$ 505.00</t>
-  </si>
-  <si>
-    <t>$ 50.50</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>VP Marketing &amp; Sales</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>O&amp;M Network Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 20.00</t>
-  </si>
-  <si>
-    <t>$ 42.59</t>
-  </si>
-  <si>
-    <t>$ 383.59</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Ermera</t>
-  </si>
-  <si>
-    <t>$ 561.00</t>
-  </si>
-  <si>
-    <t>$ 56.10</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Manufahi</t>
-  </si>
-  <si>
-    <t>$ 120.00</t>
-  </si>
-  <si>
-    <t>$ 45.44</t>
-  </si>
-  <si>
-    <t>$ 356.44</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -323,7 +323,7 @@
     <t>$ 367.81</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="3">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>21</v>
@@ -875,37 +875,37 @@
         <v>26</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -913,52 +913,52 @@
         <v>2</v>
       </c>
       <c r="B6" s="3">
-        <v>95008</v>
+        <v>999999</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>36</v>
@@ -972,7 +972,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3">
-        <v>24005</v>
+        <v>74003</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>38</v>
@@ -984,46 +984,46 @@
         <v>40</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1031,58 +1031,58 @@
         <v>4</v>
       </c>
       <c r="B8" s="3">
-        <v>92003</v>
+        <v>91015</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="O8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="S8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1090,58 +1090,58 @@
         <v>5</v>
       </c>
       <c r="B9" s="3">
-        <v>91009</v>
+        <v>26013</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -1149,58 +1149,58 @@
         <v>6</v>
       </c>
       <c r="B10" s="3">
-        <v>81010</v>
+        <v>24016</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="I10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="S10" s="3" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1208,58 +1208,58 @@
         <v>7</v>
       </c>
       <c r="B11" s="3">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="S11" s="3" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1267,58 +1267,58 @@
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <v>74003</v>
+        <v>24005</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="N12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1326,58 +1326,58 @@
         <v>9</v>
       </c>
       <c r="B13" s="3">
-        <v>91015</v>
+        <v>79001</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -1385,58 +1385,58 @@
         <v>10</v>
       </c>
       <c r="B14" s="3">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -1444,58 +1444,58 @@
         <v>11</v>
       </c>
       <c r="B15" s="3">
-        <v>24016</v>
+        <v>81010</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="O15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -1535,7 +1535,7 @@
         <v>98</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>99</v>
@@ -1586,7 +1586,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -1615,7 +1615,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="7" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
